--- a/app/DeepKids_Science_Board_Topics_L1-5.xlsx
+++ b/app/DeepKids_Science_Board_Topics_L1-5.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Counts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All topics'!$A$1:$I$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All topics'!$A$1:$I$199</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Side by side'!$A$1:$D$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Counts'!$A$1:$F$6</definedName>
   </definedNames>
@@ -551,14 +551,14 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>NIOS: Open Basic Education Level A (A 102) is "equivalent to Class 3" per the book, so its 12 lessons sit at Level 3. NIOS has nothing below Level A. Level B (≈ Class 5) book not uploaded yet.</t>
+          <t>NIOS: Open Basic Education Level A (A 102) is "equivalent to Class 3" per the book, so its 12 lessons sit at Level 3. NIOS has nothing below Level A. Level B (≈ Class 5, 15 lessons) from the uploaded book.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Still to upload if wanted: Cambridge Learner's Books 1 and 3 (2nd edition), NIOS Level B Environmental Studies.</t>
+          <t>Still to upload if wanted: Cambridge Learner's Books 1 and 3 (2nd edition).</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I185"/>
+  <dimension ref="A1:I199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6589,23 +6589,23 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Level B · Environmental Studies, ≈ Class 5</t>
+          <t>(no level)</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr"/>
       <c r="G148" s="6" t="inlineStr">
         <is>
-          <t>Level B book not uploaded yet</t>
+          <t>No NIOS level for Class 4</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
         <is>
-          <t>Upload the Level B EVS book to fill this in</t>
+          <t>Level A ≈ Class 3, Level B ≈ Class 5</t>
         </is>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>To add</t>
+          <t>From the book</t>
         </is>
       </c>
     </row>
@@ -8097,25 +8097,603 @@
           <t>Level B · Environmental Studies, ≈ Class 5</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr"/>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 1</t>
+        </is>
+      </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>Level B book not uploaded yet</t>
+          <t>India's Cultural and Natural Heritage: Its Conservation and Honour</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>Upload the Level B EVS book to fill this in</t>
+          <t>Culture and heritage and why to conserve them; India's natural heritage: forests, wildlife, water and minerals</t>
         </is>
       </c>
       <c r="I185" s="7" t="inlineStr">
         <is>
-          <t>To add</t>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B186" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C186" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 2</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>Peace, Unity and Harmony in Indian Society</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>People and customs of India; unity in diversity; peace and harmony; Ashoka and Akbar</t>
+        </is>
+      </c>
+      <c r="I186" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B187" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C187" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 3</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Our Social Issues</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>Small families; education and girls' literacy; equality of men and women; dowry and the law; female foeticide</t>
+        </is>
+      </c>
+      <c r="I187" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B188" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C188" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 4</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>Our Freedom Struggle</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>How British rule was established; people from every state in the freedom struggle; Gandhiji and other leaders; safeguarding independence</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B189" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C189" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 5</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>The States of India and their Physical Features</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
+          <t>States and Union Territories on the map; India on the world map; physical features, resources, climate, crops and vegetation</t>
+        </is>
+      </c>
+      <c r="I189" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B190" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C190" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 6</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Our Community and Public Administration</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>Democracy; the right to vote; how government works; rural and urban administration</t>
+        </is>
+      </c>
+      <c r="I190" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B191" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C191" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 7</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>Life of Plants and Animals</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>How plants and animals depend on each other; food chains and food webs; natural balance; protecting forests and animals</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B192" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C192" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 8</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>Soil and Crops</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>Types of soil and crops; preparing the field, sowing, manure and fertiliser; protecting crops; irrigation, weeding, harvesting; crops by season</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B193" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C193" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 9</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>Conservation of Soil and Forests</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>Soil erosion, its harm and prevention; soil pollution; why forests must be protected</t>
+        </is>
+      </c>
+      <c r="I193" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B194" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C194" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 10</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>Sources of Energy and their Importance</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>Why we need energy; sources and kinds of energy; alternatives; saving energy</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B195" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C195" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 11</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>Solar System and Earth</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>Planets of the solar system and Earth; planets vs satellites; phases of the Moon; natural and man-made satellites; latitude and longitude; time zones</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B196" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C196" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 12</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>Food and Health</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>Deficiency diseases and how to prevent them; when to take extra care with food; cheap nutritious foods; storing food</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B197" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C197" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 13</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>Internal Organs of the Human Body</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>The main internal organs and what each does</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B198" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C198" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 14</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>Common Diseases: their Reasons, Prevention and Protection</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>Infectious and non-infectious diseases; symptoms and spread; prevention</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B199" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C199" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>NIOS OBE</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>Level B · Environmental Studies, ≈ Class 5</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>Lesson 15</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>Garbage and Waste Disposal</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>Organic and inorganic waste; disposal and reuse; cleanliness and dustbins; harm to the environment</t>
+        </is>
+      </c>
+      <c r="I199" s="7" t="inlineStr">
+        <is>
+          <t>From the book</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I185"/>
+  <autoFilter ref="A1:I199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9079,7 +9657,7 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Level B book not uploaded yet</t>
+          <t>No NIOS level for Class 4</t>
         </is>
       </c>
     </row>
@@ -9427,7 +10005,7 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Level B book not uploaded yet</t>
+          <t>India's Cultural and Natural Heritage: Its Conservation and Honour</t>
         </is>
       </c>
     </row>
@@ -9443,7 +10021,11 @@
           <t>1.2 Pollination, fruits and seeds</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr"/>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Peace, Unity and Harmony in Indian Society</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr"/>
@@ -9457,7 +10039,11 @@
           <t>1.3 How seeds are spread</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr"/>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>Our Social Issues</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr"/>
@@ -9471,7 +10057,11 @@
           <t>1.4 Seed germination</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr"/>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>Our Freedom Struggle</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr"/>
@@ -9485,7 +10075,11 @@
           <t>2.1 How are sounds made?</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr"/>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>The States of India and their Physical Features</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr"/>
@@ -9499,7 +10093,11 @@
           <t>2.2 Volume and pitch</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr"/>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Our Community and Public Administration</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr"/>
@@ -9513,7 +10111,11 @@
           <t>2.3 Changing the volume of sound</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr"/>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Life of Plants and Animals</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr"/>
@@ -9527,7 +10129,11 @@
           <t>2.4 Changing the pitch of sound</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr"/>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Soil and Crops</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr"/>
@@ -9541,7 +10147,11 @@
           <t>3.1 Gases</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr"/>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Conservation of Soil and Forests</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr"/>
@@ -9555,7 +10165,11 @@
           <t>3.2 Properties of water</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr"/>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Sources of Energy and their Importance</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr"/>
@@ -9565,7 +10179,11 @@
           <t>3.3 Evaporation and condensation</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr"/>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Solar System and Earth</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr"/>
@@ -9575,7 +10193,11 @@
           <t>3.4 Solutions</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr"/>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Food and Health</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr"/>
@@ -9585,7 +10207,11 @@
           <t>4.1 Parts and functions of the digestive system</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr"/>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Internal Organs of the Human Body</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr"/>
@@ -9595,7 +10221,11 @@
           <t>4.2 Balanced diets</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr"/>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Common Diseases: their Reasons, Prevention and Protection</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr"/>
@@ -9605,7 +10235,11 @@
           <t>5.1 Gravity, normal forces and applied forces</t>
         </is>
       </c>
-      <c r="D124" s="7" t="inlineStr"/>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Garbage and Waste Disposal</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr"/>
@@ -9869,7 +10503,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
